--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/WYOMING_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/WYOMING_2022.xlsx
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C54">
